--- a/docs/API comparison.xlsx
+++ b/docs/API comparison.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV_ALL\taj-alwaqar\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40C706B-37F6-41A9-99D1-74EEC4DDBF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7381968-57D5-43A0-A2FA-3F5056172518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="intro" sheetId="2" r:id="rId1"/>
-    <sheet name="sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Intro" sheetId="2" r:id="rId1"/>
+    <sheet name="APIs" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Comparison of publicly available quran APIs</t>
   </si>
@@ -85,12 +85,6 @@
     <t>https://api.alquran.cloud/v1</t>
   </si>
   <si>
-    <t>Audio Mode</t>
-  </si>
-  <si>
-    <t>File per Ayah</t>
-  </si>
-  <si>
     <t>Alquran Cloud / Islamic Network</t>
   </si>
   <si>
@@ -98,6 +92,15 @@
   </si>
   <si>
     <t>Quran.com (Latest) / Quranic Audio</t>
+  </si>
+  <si>
+    <t>Audio File Mode</t>
+  </si>
+  <si>
+    <t>Surah - HTTP "Range" header for Ayah</t>
+  </si>
+  <si>
+    <t>Ayah</t>
   </si>
 </sst>
 </file>
@@ -150,13 +153,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -529,8 +531,8 @@
       <c r="D1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>19</v>
+      <c r="E1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -538,13 +540,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -552,13 +557,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -575,7 +583,7 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -583,7 +591,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>14</v>
@@ -592,7 +600,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
